--- a/st.xlsx
+++ b/st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meedoamd/Desktop/أعمالي من الهاردسك الخارجي/مدرسة الراشدية الابتدائية/عام ١٤٤٧/الفصل الثاني/لجان الاختبارات/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41B34175-4F44-7144-AC49-E283E9F37D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9082B37F-B4CE-3943-BC8E-24AA6D4DC8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16260" xr2:uid="{1B51B7E4-31C9-314E-A2A7-AA1EDB784A81}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16140" xr2:uid="{1B51B7E4-31C9-314E-A2A7-AA1EDB784A81}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="561">
   <si>
     <t>أمين فؤاد عايض الحربى</t>
   </si>
@@ -1715,6 +1715,9 @@
   </si>
   <si>
     <t>العشرون</t>
+  </si>
+  <si>
+    <t>محمد علي الكناني</t>
   </si>
 </sst>
 </file>
@@ -2078,9 +2081,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F82191A-37DB-6144-9D68-420617030CB7}">
-  <dimension ref="A1:E520"/>
+  <dimension ref="A1:E522"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10839,6 +10843,23 @@
         <v>48680</v>
       </c>
     </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A522">
+        <v>1111111111</v>
+      </c>
+      <c r="B522" t="s">
+        <v>560</v>
+      </c>
+      <c r="C522" t="s">
+        <v>539</v>
+      </c>
+      <c r="D522" t="s">
+        <v>559</v>
+      </c>
+      <c r="E522" s="1">
+        <v>48681</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
